--- a/data/trans_dic/IP18A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -663,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,1; 55,6</t>
+          <t>34,39; 55,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,28; 78,14</t>
+          <t>56,93; 77,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,74; 84,33</t>
+          <t>65,9; 83,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,19; 88,8</t>
+          <t>59,32; 95,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,5; 76,31</t>
+          <t>54,36; 75,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,65; 77,42</t>
+          <t>57,39; 77,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,94; 79,52</t>
+          <t>58,58; 78,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,1; 92,54</t>
+          <t>67,95; 97,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,07; 63,06</t>
+          <t>47,51; 63,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,29; 75,76</t>
+          <t>59,96; 75,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,12; 78,75</t>
+          <t>64,95; 78,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,41; 86,83</t>
+          <t>70,82; 94,38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -803,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,14; 78,76</t>
+          <t>63,43; 79,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,56; 78,59</t>
+          <t>63,9; 78,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,35; 82,36</t>
+          <t>67,66; 81,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,78; 75,26</t>
+          <t>63,54; 96,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,15; 74,81</t>
+          <t>59,98; 75,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,85; 82,02</t>
+          <t>67,61; 81,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,59; 80,51</t>
+          <t>65,73; 80,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,7; 78,7</t>
+          <t>81,42; 97,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,26; 74,58</t>
+          <t>64,45; 74,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68,56; 78,58</t>
+          <t>68,51; 79,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,94; 79,13</t>
+          <t>68,53; 78,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,04; 69,88</t>
+          <t>77,95; 96,04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -943,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,42; 82,59</t>
+          <t>65,0; 82,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,59; 65,39</t>
+          <t>45,23; 66,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,85; 79,55</t>
+          <t>57,89; 78,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 40,51</t>
+          <t>63,39; 96,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,61; 82,23</t>
+          <t>65,45; 81,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,18; 64,33</t>
+          <t>44,43; 64,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,07; 86,12</t>
+          <t>69,05; 85,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>72,64; 97,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67,3; 79,98</t>
+          <t>67,73; 80,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,31; 62,35</t>
+          <t>48,45; 62,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67,11; 80,18</t>
+          <t>66,2; 80,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 20,64</t>
+          <t>75,28; 95,51</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>82,85%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,64; 73,23</t>
+          <t>55,52; 74,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,11; 88,23</t>
+          <t>72,59; 87,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,83; 81,32</t>
+          <t>63,32; 81,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 51,8</t>
+          <t>49,56; 93,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,27; 74,19</t>
+          <t>55,45; 74,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,55; 85,95</t>
+          <t>70,3; 86,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,22; 82,25</t>
+          <t>63,62; 81,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,92</t>
+          <t>63,21; 97,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,78; 71,22</t>
+          <t>58,41; 71,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,93; 85,54</t>
+          <t>74,29; 85,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,84; 78,88</t>
+          <t>65,8; 78,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 51,09</t>
+          <t>66,69; 93,03</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,24; 57,11</t>
+          <t>28,95; 57,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,43; 96,36</t>
+          <t>79,37; 96,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,36; 81,84</t>
+          <t>59,33; 82,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,1</t>
+          <t>38,38; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,16; 71,67</t>
+          <t>43,65; 72,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,76; 87,38</t>
+          <t>63,74; 86,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,96; 74,89</t>
+          <t>51,85; 74,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 65,27</t>
+          <t>42,83; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,11; 59,93</t>
+          <t>39,71; 61,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75,59; 89,33</t>
+          <t>75,4; 89,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,43; 75,23</t>
+          <t>58,83; 75,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 58,85</t>
+          <t>56,76; 94,71</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,34; 85,44</t>
+          <t>65,18; 84,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,72; 66,89</t>
+          <t>45,32; 66,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,91; 79,45</t>
+          <t>59,2; 80,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 45,95</t>
+          <t>56,17; 96,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,53; 80,05</t>
+          <t>59,48; 80,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,13; 61,03</t>
+          <t>38,33; 60,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,66; 79,4</t>
+          <t>58,65; 78,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,24</t>
+          <t>65,36; 94,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,14; 79,62</t>
+          <t>66,52; 80,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,63; 59,89</t>
+          <t>44,45; 59,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61,64; 76,47</t>
+          <t>62,12; 76,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 25,01</t>
+          <t>68,43; 92,33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1503,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>63,34; 76,84</t>
+          <t>63,53; 76,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,46; 58,56</t>
+          <t>44,09; 58,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,73; 51,6</t>
+          <t>35,89; 51,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,84; 61,67</t>
+          <t>59,51; 91,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,81; 73,13</t>
+          <t>59,34; 73,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,24; 61,37</t>
+          <t>47,89; 61,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,05; 54,37</t>
+          <t>38,41; 54,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,69; 43,81</t>
+          <t>62,76; 89,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63,28; 72,95</t>
+          <t>62,89; 72,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,22; 57,8</t>
+          <t>47,95; 57,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,75; 50,33</t>
+          <t>39,85; 50,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,39; 46,05</t>
+          <t>67,19; 87,35</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,68; 56,43</t>
+          <t>41,87; 55,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59,51; 71,39</t>
+          <t>59,77; 72,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56,12; 68,13</t>
+          <t>55,6; 68,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,88; 59,54</t>
+          <t>21,04; 61,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,36; 59,75</t>
+          <t>44,99; 58,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,55; 75,81</t>
+          <t>64,63; 76,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,82; 65,89</t>
+          <t>53,51; 65,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,68; 60,34</t>
+          <t>29,12; 65,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45,71; 55,87</t>
+          <t>45,67; 55,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63,22; 72,06</t>
+          <t>63,49; 72,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56,54; 65,4</t>
+          <t>56,86; 65,67</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,55; 53,54</t>
+          <t>31,44; 59,25</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59,51; 65,82</t>
+          <t>59,6; 66,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62,23; 68,19</t>
+          <t>61,9; 68,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62,1; 68,02</t>
+          <t>62,04; 68,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29,25; 45,82</t>
+          <t>69,78; 83,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61,16; 67,32</t>
+          <t>60,91; 67,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,72; 68,79</t>
+          <t>62,89; 68,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,87; 67,93</t>
+          <t>61,77; 67,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25,06; 39,72</t>
+          <t>73,5; 84,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>61,38; 65,82</t>
+          <t>61,45; 65,85</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63,41; 67,63</t>
+          <t>63,41; 67,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62,88; 67,16</t>
+          <t>62,75; 67,01</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,45; 40,44</t>
+          <t>73,63; 82,62</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22636</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35728</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40304</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10055</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34078</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40003</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39349</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12366</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>56714</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>75730</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79653</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>22421</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17278; 27952</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29546; 40386</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35237; 44816</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7172; 11503</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28278; 39197</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>33660; 45414</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>33342; 44548</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9557; 13655</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>48583; 64703</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>66289; 83294</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>71690; 86804</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>18524; 24686</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>65834</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>68419</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67609</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11599</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65910</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74174</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69149</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15157</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>131744</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>142593</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>136758</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26756</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>58068; 72832</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>60883; 75215</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>60725; 73499</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8660; 13207</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>57985; 72648</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>66348; 79684</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>62095; 76114</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13295; 15984</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>121309; 141107</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>132512; 152830</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>126249; 145152</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>23352; 28771</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>47237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37469</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46174</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12108</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49652</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39002</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48689</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14677</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>96889</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>76471</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>94863</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>26785</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>41178; 52505</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30492; 45159</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38243; 51539</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8848; 13405</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>43951; 54719</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31366; 45309</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>42833; 52975</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>11928; 16091</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>88389; 104909</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>66875; 85798</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>84807; 102708</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>22870; 29016</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>43401</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58762</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53307</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44451</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62816</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58131</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12855</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>87852</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>121577</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>111439</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>23167</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>37418; 50051</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>52504; 63534</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>46387; 59417</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6576; 12403</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>37580; 50491</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>55699; 68217</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>50346; 64179</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9289; 14261</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>78948; 96910</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>112593; 129064</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>100282; 120127</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>18648; 26013</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>13379</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29932</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18710</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33153</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28654</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>32090</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>68905</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>58587</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>7603</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9297; 18317</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31371; 38118</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24805; 34332</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1523; 3968</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>14041; 23456</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>27585; 37289</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23271; 33456</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2294; 5357</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>25525; 39392</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>62432; 74131</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>50999; 65350</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5293; 8831</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>38792</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>30697</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>36481</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7631</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>35927</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>28982</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>39918</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>14249</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>74720</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>59680</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>76399</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>21880</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>33309; 43409</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>25041; 36828</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>30919; 41899</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5130; 8785</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>30222; 40789</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22646; 35744</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>33442; 44926</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>11146; 16144</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>67791; 81745</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>50823; 67915</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>67867; 83937</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>17921; 24180</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>84998</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>69090</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>48163</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17350</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>83096</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>77421</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>52786</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>21860</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>168094</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>146511</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>100949</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>39211</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>77271; 93210</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>59228; 78072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>40039; 57108</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13265; 20486</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>73490; 90591</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>68212; 87650</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>43182; 61618</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>17401; 24771</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>154382; 177888</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>132705; 159853</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>89252; 113129</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>33607; 43689</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>59308</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>99762</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>99185</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>69777</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>113289</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99317</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>9184</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>129085</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>213051</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>198502</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>50509; 67481</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>90824; 109744</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>88479; 108554</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2520; 7333</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>60089; 78761</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>103947; 122564</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>88302; 108777</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>5807; 13003</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>116097; 141730</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>198596; 225848</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>184329; 212886</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>10035; 18911</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>375587</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>435678</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>421157</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>77333</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>104593</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>777188</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>904518</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>857149</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>181926</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>356422; 394946</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>413497; 454263</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>401597; 440376</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>69996; 84020</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>380118; 422228</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>447890; 490760</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>415013; 455541</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>96721; 111564</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>750925; 804747</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>875216; 931656</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>827832; 884042</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>170762; 191593</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,39; 55,64</t>
+          <t>33,99; 55,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,93; 77,82</t>
+          <t>56,73; 78,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,9; 83,82</t>
+          <t>65,46; 83,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,32; 95,14</t>
+          <t>56,92; 95,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,36; 75,35</t>
+          <t>54,29; 75,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,39; 77,43</t>
+          <t>56,92; 77,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,58; 78,27</t>
+          <t>58,48; 78,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,95; 97,09</t>
+          <t>67,41; 97,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,51; 63,27</t>
+          <t>46,99; 62,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,96; 75,35</t>
+          <t>60,29; 75,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,95; 78,64</t>
+          <t>65,83; 79,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,82; 94,38</t>
+          <t>71,01; 94,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,43; 79,55</t>
+          <t>64,14; 78,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,9; 78,94</t>
+          <t>63,17; 78,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,66; 81,9</t>
+          <t>67,83; 81,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,54; 96,9</t>
+          <t>63,67; 97,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,98; 75,15</t>
+          <t>60,13; 75,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,61; 81,2</t>
+          <t>68,33; 82,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,73; 80,57</t>
+          <t>65,01; 80,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,42; 97,88</t>
+          <t>79,45; 97,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,45; 74,97</t>
+          <t>64,72; 75,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68,51; 79,02</t>
+          <t>69,06; 78,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,53; 78,79</t>
+          <t>68,57; 79,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,95; 96,04</t>
+          <t>76,31; 96,05</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,0; 82,88</t>
+          <t>64,2; 82,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,23; 66,99</t>
+          <t>44,91; 65,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,89; 78,01</t>
+          <t>59,16; 78,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,39; 96,04</t>
+          <t>69,08; 96,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,45; 81,49</t>
+          <t>65,52; 81,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,43; 64,17</t>
+          <t>46,07; 65,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,05; 85,4</t>
+          <t>69,99; 86,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,64; 97,98</t>
+          <t>70,76; 97,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67,73; 80,39</t>
+          <t>67,61; 80,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,45; 62,16</t>
+          <t>48,71; 62,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,2; 80,18</t>
+          <t>67,31; 80,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,28; 95,51</t>
+          <t>76,92; 95,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,52; 74,26</t>
+          <t>54,89; 73,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,59; 87,83</t>
+          <t>73,2; 88,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,32; 81,1</t>
+          <t>62,69; 80,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,56; 93,48</t>
+          <t>48,9; 94,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,45; 74,5</t>
+          <t>55,69; 74,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,3; 86,1</t>
+          <t>70,67; 85,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,62; 81,1</t>
+          <t>62,95; 80,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,21; 97,05</t>
+          <t>64,82; 97,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,41; 71,7</t>
+          <t>58,26; 71,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,29; 85,16</t>
+          <t>73,93; 85,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,8; 78,82</t>
+          <t>66,4; 78,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,69; 93,03</t>
+          <t>66,09; 93,36</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,95; 57,05</t>
+          <t>27,85; 56,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,37; 96,44</t>
+          <t>79,78; 96,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,33; 82,12</t>
+          <t>58,65; 81,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,65; 72,92</t>
+          <t>42,68; 71,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,74; 86,16</t>
+          <t>64,2; 86,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,85; 74,54</t>
+          <t>51,37; 74,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,83; 100,0</t>
+          <t>44,28; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,71; 61,29</t>
+          <t>40,36; 60,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75,4; 89,53</t>
+          <t>75,8; 89,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,83; 75,38</t>
+          <t>58,27; 75,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,76; 94,71</t>
+          <t>57,06; 94,69</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,18; 84,94</t>
+          <t>65,02; 85,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,32; 66,65</t>
+          <t>43,57; 66,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,2; 80,22</t>
+          <t>58,29; 79,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,17; 96,18</t>
+          <t>56,32; 96,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,48; 80,28</t>
+          <t>59,65; 80,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,33; 60,5</t>
+          <t>38,78; 60,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,65; 78,79</t>
+          <t>59,35; 78,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,36; 94,66</t>
+          <t>64,08; 93,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66,52; 80,21</t>
+          <t>66,43; 80,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,45; 59,4</t>
+          <t>44,68; 59,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,12; 76,83</t>
+          <t>62,08; 75,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68,43; 92,33</t>
+          <t>69,46; 92,28</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>63,53; 76,64</t>
+          <t>62,6; 76,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,09; 58,11</t>
+          <t>44,35; 58,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,89; 51,2</t>
+          <t>36,35; 51,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59,51; 91,9</t>
+          <t>60,16; 91,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,34; 73,15</t>
+          <t>60,02; 73,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,89; 61,54</t>
+          <t>47,6; 61,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,41; 54,81</t>
+          <t>39,26; 54,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,76; 89,34</t>
+          <t>61,29; 89,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>62,89; 72,47</t>
+          <t>63,37; 72,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47,95; 57,75</t>
+          <t>48,34; 58,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,85; 50,51</t>
+          <t>39,79; 50,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,19; 87,35</t>
+          <t>66,92; 87,11</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,87; 55,93</t>
+          <t>41,41; 56,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59,77; 72,22</t>
+          <t>58,93; 71,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55,6; 68,21</t>
+          <t>55,62; 67,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,04; 61,22</t>
+          <t>22,38; 65,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,99; 58,96</t>
+          <t>45,05; 58,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,63; 76,21</t>
+          <t>64,54; 75,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,51; 65,92</t>
+          <t>54,08; 66,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,12; 65,2</t>
+          <t>28,17; 64,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45,67; 55,75</t>
+          <t>46,07; 55,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63,49; 72,21</t>
+          <t>63,74; 72,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56,86; 65,67</t>
+          <t>56,78; 65,1</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,44; 59,25</t>
+          <t>30,47; 58,53</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59,6; 66,04</t>
+          <t>59,76; 66,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61,9; 68,0</t>
+          <t>62,21; 67,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62,04; 68,04</t>
+          <t>62,12; 68,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69,78; 83,76</t>
+          <t>69,12; 83,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60,91; 67,66</t>
+          <t>61,26; 67,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,89; 68,9</t>
+          <t>62,72; 68,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,77; 67,8</t>
+          <t>61,91; 67,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>73,5; 84,78</t>
+          <t>73,8; 85,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>61,45; 65,85</t>
+          <t>61,26; 65,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63,41; 67,5</t>
+          <t>63,39; 67,62</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62,75; 67,01</t>
+          <t>62,82; 67,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73,63; 82,62</t>
+          <t>73,72; 83,08</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17278; 27952</t>
+          <t>17076; 27861</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29546; 40386</t>
+          <t>29443; 40828</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35237; 44816</t>
+          <t>35002; 44802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7172; 11503</t>
+          <t>6883; 11488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28278; 39197</t>
+          <t>28240; 39208</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33660; 45414</t>
+          <t>33382; 45420</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33342; 44548</t>
+          <t>33282; 44676</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9557; 13655</t>
+          <t>9480; 13658</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48583; 64703</t>
+          <t>48050; 64200</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66289; 83294</t>
+          <t>66653; 82997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71690; 86804</t>
+          <t>72663; 87933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18524; 24686</t>
+          <t>18571; 24638</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58068; 72832</t>
+          <t>58724; 72047</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60883; 75215</t>
+          <t>60190; 74957</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60725; 73499</t>
+          <t>60872; 73273</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8660; 13207</t>
+          <t>8677; 13232</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57985; 72648</t>
+          <t>58129; 72959</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66348; 79684</t>
+          <t>67050; 80563</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62095; 76114</t>
+          <t>61412; 75797</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13295; 15984</t>
+          <t>12974; 15978</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121309; 141107</t>
+          <t>121822; 142305</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132512; 152830</t>
+          <t>133566; 152703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126249; 145152</t>
+          <t>126309; 146475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23352; 28771</t>
+          <t>22861; 28774</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41178; 52505</t>
+          <t>40671; 52213</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30492; 45159</t>
+          <t>30276; 43906</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38243; 51539</t>
+          <t>39085; 52121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8848; 13405</t>
+          <t>9641; 13429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43951; 54719</t>
+          <t>43997; 54726</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31366; 45309</t>
+          <t>32525; 46167</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42833; 52975</t>
+          <t>43417; 53529</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11928; 16091</t>
+          <t>11621; 16037</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88389; 104909</t>
+          <t>88236; 104609</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66875; 85798</t>
+          <t>67229; 86247</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84807; 102708</t>
+          <t>86221; 103024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22870; 29016</t>
+          <t>23366; 29024</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37418; 50051</t>
+          <t>36994; 49729</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52504; 63534</t>
+          <t>52946; 63884</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46387; 59417</t>
+          <t>45930; 58882</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6576; 12403</t>
+          <t>6488; 12504</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37580; 50491</t>
+          <t>37743; 50579</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55699; 68217</t>
+          <t>55987; 67813</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50346; 64179</t>
+          <t>49819; 64017</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9289; 14261</t>
+          <t>9525; 14272</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78948; 96910</t>
+          <t>78749; 96516</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112593; 129064</t>
+          <t>112057; 129658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100282; 120127</t>
+          <t>101195; 119903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18648; 26013</t>
+          <t>18481; 26106</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9297; 18317</t>
+          <t>8942; 18278</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31371; 38118</t>
+          <t>31531; 38105</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24805; 34332</t>
+          <t>24522; 34005</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14041; 23456</t>
+          <t>13728; 23031</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27585; 37289</t>
+          <t>27785; 37348</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23271; 33456</t>
+          <t>23058; 33320</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2294; 5357</t>
+          <t>2372; 5357</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25525; 39392</t>
+          <t>25943; 38756</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62432; 74131</t>
+          <t>62769; 74262</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50999; 65350</t>
+          <t>50517; 65850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5293; 8831</t>
+          <t>5320; 8829</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33309; 43409</t>
+          <t>33231; 43494</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25041; 36828</t>
+          <t>24074; 36479</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30919; 41899</t>
+          <t>30446; 41450</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5130; 8785</t>
+          <t>5144; 8772</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30222; 40789</t>
+          <t>30308; 40751</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22646; 35744</t>
+          <t>22910; 35963</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33442; 44926</t>
+          <t>33844; 44982</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11146; 16144</t>
+          <t>10928; 15911</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67791; 81745</t>
+          <t>67700; 82026</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50823; 67915</t>
+          <t>51091; 68046</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67867; 83937</t>
+          <t>67827; 82966</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17921; 24180</t>
+          <t>18190; 24166</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>77271; 93210</t>
+          <t>76136; 93002</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59228; 78072</t>
+          <t>59587; 77978</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40039; 57108</t>
+          <t>40549; 57555</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13265; 20486</t>
+          <t>13410; 20434</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>73490; 90591</t>
+          <t>74336; 91280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>68212; 87650</t>
+          <t>67796; 87865</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43182; 61618</t>
+          <t>44145; 61334</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17401; 24771</t>
+          <t>16994; 24949</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154382; 177888</t>
+          <t>155559; 178709</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>132705; 159853</t>
+          <t>133790; 160798</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>89252; 113129</t>
+          <t>89116; 112862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33607; 43689</t>
+          <t>33469; 43571</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>50509; 67481</t>
+          <t>49954; 67570</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>90824; 109744</t>
+          <t>89545; 108919</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>88479; 108554</t>
+          <t>88520; 108094</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2520; 7333</t>
+          <t>2681; 7811</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60089; 78761</t>
+          <t>60179; 78559</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>103947; 122564</t>
+          <t>103797; 121869</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>88302; 108777</t>
+          <t>89237; 109396</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5807; 13003</t>
+          <t>5617; 12890</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>116097; 141730</t>
+          <t>117126; 141824</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>198596; 225848</t>
+          <t>199375; 227221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>184329; 212886</t>
+          <t>184063; 211010</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10035; 18911</t>
+          <t>9727; 18684</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>356422; 394946</t>
+          <t>357395; 395617</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>413497; 454263</t>
+          <t>415593; 454096</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>401597; 440376</t>
+          <t>402102; 441011</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69996; 84020</t>
+          <t>69339; 83614</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>380118; 422228</t>
+          <t>382268; 419985</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>447890; 490760</t>
+          <t>446708; 490247</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>415013; 455541</t>
+          <t>415971; 454660</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>96721; 111564</t>
+          <t>97109; 111974</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>750925; 804747</t>
+          <t>748592; 803506</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>875216; 931656</t>
+          <t>874944; 933318</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>827832; 884042</t>
+          <t>828723; 884751</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>170762; 191593</t>
+          <t>170971; 192659</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>65,51%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69,14%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>45,06%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>68,85%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>75,38%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83,16%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,14%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,99; 55,46</t>
+          <t>54,5; 76,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,73; 78,67</t>
+          <t>56,65; 77,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,46; 83,79</t>
+          <t>58,94; 79,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,92; 95,01</t>
+          <t>69,44; 97,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,29; 75,38</t>
+          <t>33,1; 55,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,92; 77,44</t>
+          <t>57,28; 78,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,48; 78,49</t>
+          <t>65,74; 84,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,41; 97,12</t>
+          <t>55,11; 94,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,99; 62,78</t>
+          <t>48,07; 63,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,29; 75,08</t>
+          <t>61,29; 75,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,83; 79,66</t>
+          <t>65,12; 78,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,01; 94,2</t>
+          <t>68,41; 93,12</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73,2%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>71,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>71,81%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>75,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>85,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>75,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,14; 78,7</t>
+          <t>60,15; 74,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,17; 78,67</t>
+          <t>67,85; 82,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,83; 81,64</t>
+          <t>65,59; 80,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,67; 97,09</t>
+          <t>82,56; 98,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,13; 75,47</t>
+          <t>64,14; 78,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,33; 82,1</t>
+          <t>63,56; 78,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,01; 80,23</t>
+          <t>67,35; 82,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,45; 97,85</t>
+          <t>60,4; 97,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,72; 75,6</t>
+          <t>64,26; 74,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,06; 78,95</t>
+          <t>68,56; 78,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,57; 79,51</t>
+          <t>68,94; 79,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,31; 96,05</t>
+          <t>75,89; 95,84</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73,94%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78,49%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90,01%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>74,56%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>55,58%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>69,89%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>86,75%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,49%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,2; 82,42</t>
+          <t>64,61; 82,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,91; 65,13</t>
+          <t>45,18; 64,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,16; 78,89</t>
+          <t>69,07; 86,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,08; 96,22</t>
+          <t>73,82; 97,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,52; 81,5</t>
+          <t>64,42; 82,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,07; 65,39</t>
+          <t>45,59; 65,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,99; 86,29</t>
+          <t>59,85; 79,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,76; 97,66</t>
+          <t>65,23; 96,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67,61; 80,16</t>
+          <t>67,3; 79,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,71; 62,49</t>
+          <t>48,31; 62,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67,31; 80,42</t>
+          <t>67,11; 80,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76,92; 95,54</t>
+          <t>77,11; 94,87</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>64,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>81,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>72,76%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,46%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,89; 73,79</t>
+          <t>57,27; 74,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,2; 88,32</t>
+          <t>71,55; 85,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,69; 80,37</t>
+          <t>65,22; 82,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,9; 94,24</t>
+          <t>68,01; 97,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,69; 74,63</t>
+          <t>54,64; 73,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,67; 85,59</t>
+          <t>73,11; 88,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,95; 80,9</t>
+          <t>62,83; 81,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,82; 97,12</t>
+          <t>46,82; 94,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,26; 71,4</t>
+          <t>57,78; 71,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,93; 85,55</t>
+          <t>73,93; 85,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,4; 78,68</t>
+          <t>66,84; 78,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,09; 93,36</t>
+          <t>64,91; 93,33</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>58,17%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76,6%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>63,84%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>78,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>41,67%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>90,45%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>71,59%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>58,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>76,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>63,84%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,85; 56,93</t>
+          <t>43,16; 71,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,78; 96,41</t>
+          <t>64,76; 87,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,65; 81,33</t>
+          <t>50,96; 74,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,38; 100,0</t>
+          <t>43,62; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,68; 71,6</t>
+          <t>28,24; 57,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,2; 86,3</t>
+          <t>79,43; 96,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,37; 74,24</t>
+          <t>59,36; 81,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,28; 100,0</t>
+          <t>52,22; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,36; 60,3</t>
+          <t>39,11; 59,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75,8; 89,69</t>
+          <t>75,59; 89,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,27; 75,96</t>
+          <t>59,43; 75,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,06; 94,69</t>
+          <t>58,77; 94,69</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>70,71%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>75,9%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>55,55%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>69,85%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>83,55%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,02; 85,1</t>
+          <t>60,53; 80,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,57; 66,01</t>
+          <t>38,13; 61,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,29; 79,36</t>
+          <t>58,66; 79,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,32; 96,05</t>
+          <t>62,55; 93,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,65; 80,2</t>
+          <t>65,34; 85,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,78; 60,87</t>
+          <t>44,72; 66,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,35; 78,88</t>
+          <t>57,91; 79,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,08; 93,29</t>
+          <t>60,64; 97,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66,43; 80,48</t>
+          <t>65,14; 79,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,68; 59,51</t>
+          <t>44,63; 59,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,08; 75,94</t>
+          <t>61,64; 76,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,46; 92,28</t>
+          <t>68,48; 92,65</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67,09%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46,95%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>79,47%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>69,89%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>51,43%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>43,18%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>77,84%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>67,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,95%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,6; 76,47</t>
+          <t>59,81; 73,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,35; 58,04</t>
+          <t>47,24; 61,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,35; 51,6</t>
+          <t>39,05; 54,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,16; 91,67</t>
+          <t>63,81; 90,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,02; 73,7</t>
+          <t>63,34; 76,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,6; 61,69</t>
+          <t>44,46; 58,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,26; 54,55</t>
+          <t>35,73; 51,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61,29; 89,98</t>
+          <t>55,55; 87,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63,37; 72,8</t>
+          <t>63,28; 72,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,34; 58,1</t>
+          <t>48,22; 57,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,79; 50,39</t>
+          <t>39,75; 50,33</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,92; 87,11</t>
+          <t>65,41; 86,98</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>52,24%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70,44%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>60,19%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>49,16%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>65,65%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>62,32%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>52,24%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>60,19%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,41; 56,01</t>
+          <t>45,36; 59,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58,93; 71,68</t>
+          <t>64,55; 75,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55,62; 67,92</t>
+          <t>53,82; 65,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,38; 65,21</t>
+          <t>29,75; 68,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,05; 58,81</t>
+          <t>42,68; 56,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,54; 75,78</t>
+          <t>59,51; 71,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,08; 66,3</t>
+          <t>56,12; 68,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,17; 64,64</t>
+          <t>16,15; 59,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,07; 55,79</t>
+          <t>45,71; 55,87</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63,74; 72,65</t>
+          <t>63,22; 72,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56,78; 65,1</t>
+          <t>56,54; 65,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,47; 58,53</t>
+          <t>29,55; 58,6</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>65,83%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>65,22%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>65,07%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>65,83%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59,76; 66,15</t>
+          <t>61,16; 67,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62,21; 67,98</t>
+          <t>62,72; 68,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62,12; 68,13</t>
+          <t>61,87; 67,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69,12; 83,35</t>
+          <t>72,99; 84,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61,26; 67,3</t>
+          <t>59,51; 65,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,72; 68,83</t>
+          <t>62,23; 68,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,91; 67,67</t>
+          <t>62,1; 68,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>73,8; 85,09</t>
+          <t>67,41; 82,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>61,26; 65,75</t>
+          <t>61,38; 65,82</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63,39; 67,62</t>
+          <t>63,41; 67,63</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62,82; 67,07</t>
+          <t>62,88; 67,16</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73,72; 83,08</t>
+          <t>72,72; 82,04</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34078</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40003</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39349</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10652</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22636</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>35728</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>40304</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10055</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34078</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40003</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39349</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>19824</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17076; 27861</t>
+          <t>28350; 39695</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29443; 40828</t>
+          <t>33227; 45407</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35002; 44802</t>
+          <t>33544; 45262</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6883; 11488</t>
+          <t>8458; 11861</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28240; 39208</t>
+          <t>16630; 27935</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33382; 45420</t>
+          <t>29725; 40549</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33282; 44676</t>
+          <t>35148; 45090</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9480; 13658</t>
+          <t>6124; 10539</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48050; 64200</t>
+          <t>49155; 64488</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66653; 82997</t>
+          <t>67752; 83751</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72663; 87933</t>
+          <t>71888; 86932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18571; 24638</t>
+          <t>15935; 21690</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65910</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74174</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69149</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13536</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>65834</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>68419</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>67609</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11599</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65910</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74174</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69149</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26756</t>
+          <t>24603</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58724; 72047</t>
+          <t>58144; 72323</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60190; 74957</t>
+          <t>66580; 80490</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60872; 73273</t>
+          <t>61963; 76061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8677; 13232</t>
+          <t>11906; 14164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58129; 72959</t>
+          <t>58720; 72107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67050; 80563</t>
+          <t>60565; 74878</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61412; 75797</t>
+          <t>60447; 73914</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12974; 15978</t>
+          <t>7920; 12750</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121822; 142305</t>
+          <t>120951; 140381</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133566; 152703</t>
+          <t>132608; 151977</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126309; 146475</t>
+          <t>127003; 145768</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22861; 28774</t>
+          <t>20893; 26385</t>
         </is>
       </c>
     </row>
@@ -2489,37 +2489,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49652</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39002</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48689</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12639</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>47237</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>37469</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>46174</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12108</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>49652</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39002</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48689</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26785</t>
+          <t>24439</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40671; 52213</t>
+          <t>43385; 55216</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30276; 43906</t>
+          <t>31896; 45421</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39085; 52121</t>
+          <t>42850; 53423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9641; 13429</t>
+          <t>10365; 13751</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43997; 54726</t>
+          <t>40808; 52322</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32525; 46167</t>
+          <t>30731; 44080</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43417; 53529</t>
+          <t>39543; 52555</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11621; 16037</t>
+          <t>8852; 13097</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88236; 104609</t>
+          <t>87824; 104372</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67229; 86247</t>
+          <t>66675; 86053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86221; 103024</t>
+          <t>85968; 102707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23366; 29024</t>
+          <t>21293; 26195</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44451</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62816</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>58131</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12361</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>43401</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>58762</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>53307</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10312</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44451</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62816</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58131</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>22233</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36994; 49729</t>
+          <t>38812; 50284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52946; 63884</t>
+          <t>56688; 68097</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45930; 58882</t>
+          <t>51613; 65086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6488; 12504</t>
+          <t>9477; 13572</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37743; 50579</t>
+          <t>36828; 49356</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55987; 67813</t>
+          <t>52880; 63819</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49819; 64017</t>
+          <t>46029; 59574</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9525; 14272</t>
+          <t>6194; 12535</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78749; 96516</t>
+          <t>78094; 96267</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112057; 129658</t>
+          <t>112057; 129642</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101195; 119903</t>
+          <t>101860; 120205</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18481; 26106</t>
+          <t>17633; 25352</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>18710</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33153</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28654</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>13379</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>29932</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3360</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18710</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33153</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28654</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7835</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8942; 18278</t>
+          <t>13883; 23053</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31531; 38105</t>
+          <t>28025; 37816</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24522; 34005</t>
+          <t>22873; 33611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1523; 3968</t>
+          <t>2342; 5368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13728; 23031</t>
+          <t>9068; 18337</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27785; 37348</t>
+          <t>31396; 38087</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23058; 33320</t>
+          <t>24816; 34216</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2372; 5357</t>
+          <t>2212; 4236</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25943; 38756</t>
+          <t>25140; 38517</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62769; 74262</t>
+          <t>62591; 73965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50517; 65850</t>
+          <t>51519; 65222</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5320; 8829</t>
+          <t>5644; 9094</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>35927</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>28982</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>39918</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11805</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>38792</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>30697</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7631</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>35927</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>28982</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>39918</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>19504</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33231; 43494</t>
+          <t>30753; 40673</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24074; 36479</t>
+          <t>22527; 36057</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30446; 41450</t>
+          <t>33452; 45275</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5144; 8772</t>
+          <t>9061; 13568</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30308; 40751</t>
+          <t>33392; 43665</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22910; 35963</t>
+          <t>24714; 36962</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33844; 44982</t>
+          <t>30247; 41494</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10928; 15911</t>
+          <t>5467; 8761</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67700; 82026</t>
+          <t>66384; 81144</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51091; 68046</t>
+          <t>51026; 68482</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67827; 82966</t>
+          <t>67340; 83545</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18190; 24166</t>
+          <t>16093; 21774</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>83096</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>77421</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>52786</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>22135</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>84998</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>69090</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>48163</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17350</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>83096</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>77421</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>52786</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>36815</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>76136; 93002</t>
+          <t>74071; 90566</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59587; 77978</t>
+          <t>67282; 87415</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40549; 57555</t>
+          <t>43907; 61134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13410; 20434</t>
+          <t>17773; 25130</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74336; 91280</t>
+          <t>77033; 93451</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67796; 87865</t>
+          <t>59729; 78680</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44145; 61334</t>
+          <t>39857; 57560</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16994; 24949</t>
+          <t>11024; 17437</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155559; 178709</t>
+          <t>155338; 179061</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>133790; 160798</t>
+          <t>133455; 159969</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>89116; 112862</t>
+          <t>89033; 112737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33469; 43571</t>
+          <t>31196; 41483</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>69777</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>113289</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>99317</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9080</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>59308</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>99762</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>99185</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4919</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>69777</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>113289</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99317</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>13351</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49954; 67570</t>
+          <t>60585; 79808</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>89545; 108919</t>
+          <t>103811; 121918</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>88520; 108094</t>
+          <t>88804; 108727</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2681; 7811</t>
+          <t>5784; 13359</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60179; 78559</t>
+          <t>51484; 68083</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>103797; 121869</t>
+          <t>90438; 108481</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>89237; 109396</t>
+          <t>89316; 108430</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5617; 12890</t>
+          <t>1839; 6765</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>117126; 141824</t>
+          <t>116202; 142029</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>199375; 227221</t>
+          <t>197725; 225391</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>184063; 211010</t>
+          <t>183277; 211994</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9727; 18684</t>
+          <t>9110; 18066</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>629</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>96443</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>375587</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>435678</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>421157</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>401602</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>468840</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>435992</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>168605</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>357395; 395617</t>
+          <t>381638; 420087</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>415593; 454096</t>
+          <t>446719; 489949</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>402102; 441011</t>
+          <t>415725; 456400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69339; 83614</t>
+          <t>88848; 103108</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>382268; 419985</t>
+          <t>355869; 393637</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>446708; 490247</t>
+          <t>415703; 455491</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>415971; 454660</t>
+          <t>401981; 440299</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>97109; 111974</t>
+          <t>64389; 78663</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>748592; 803506</t>
+          <t>750086; 804351</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>874944; 933318</t>
+          <t>875273; 933404</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>828723; 884751</t>
+          <t>829481; 885929</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>170971; 192659</t>
+          <t>157965; 178217</t>
         </is>
       </c>
     </row>
